--- a/dcf/TXN.xlsx
+++ b/dcf/TXN.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.08604999113861814</v>
+        <v>0.08605981269934165</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.09104999113861814</v>
+        <v>0.09105981269934166</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.09604999113861813</v>
+        <v>0.09605981269934165</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.1010499911386181</v>
+        <v>0.1010598126993417</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.1060499911386181</v>
+        <v>0.1060598126993417</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.1110499911386181</v>
+        <v>0.1110598126993416</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.1160499911386181</v>
+        <v>0.1160598126993417</v>
       </c>
     </row>
     <row r="5">
@@ -1125,25 +1125,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>143.5482078316294</v>
+        <v>143.5363962240959</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>137.6753133809747</v>
+        <v>137.6640488153423</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>132.0736547577069</v>
+        <v>132.062908952836</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>126.7292443521726</v>
+        <v>126.7189906235079</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>121.6288823557648</v>
+        <v>121.6190955180466</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>116.7601088660432</v>
+        <v>116.7507651423715</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>112.1111591105879</v>
+        <v>112.1022360473902</v>
       </c>
     </row>
     <row r="6">
@@ -1151,25 +1151,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>154.471785056908</v>
+        <v>154.458985638115</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>148.1084896800385</v>
+        <v>148.0962859731916</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>142.0405390925289</v>
+        <v>142.0289002121945</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>136.2526584693704</v>
+        <v>136.2415552769934</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>130.7304349093661</v>
+        <v>130.7198399066812</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>125.4602649639879</v>
+        <v>125.4501521933987</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>120.4293055863502</v>
+        <v>120.4196505377823</v>
       </c>
     </row>
     <row r="7">
@@ -1177,25 +1177,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>165.3953622821865</v>
+        <v>165.3815750521341</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>158.5416659791023</v>
+        <v>158.5285231310408</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>152.0074234273509</v>
+        <v>151.994891471553</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>145.7760725865683</v>
+        <v>145.7641199304788</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>139.8319874629673</v>
+        <v>139.8205842953157</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>134.1604210619326</v>
+        <v>134.1495392444259</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>128.7474520621125</v>
+        <v>128.7370650281745</v>
       </c>
     </row>
     <row r="8">
@@ -1203,25 +1203,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>176.318939507465</v>
+        <v>176.3041644661533</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>168.9748422781662</v>
+        <v>168.9607602888901</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>161.9743077621729</v>
+        <v>161.9608827309114</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>155.2994867037661</v>
+        <v>155.2866845839643</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>148.9335400165686</v>
+        <v>148.9213286839502</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>142.8605771598772</v>
+        <v>142.8489262954531</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>137.0655985378748</v>
+        <v>137.0544795185666</v>
       </c>
     </row>
     <row r="9">
@@ -1229,25 +1229,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>187.2425167327436</v>
+        <v>187.2267538801725</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>179.40801857723</v>
+        <v>179.3929974467394</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>171.9411920969949</v>
+        <v>171.9268739902699</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>164.822900820964</v>
+        <v>164.8092492374497</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>158.0350925701699</v>
+        <v>158.0220730725847</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>151.5607332578219</v>
+        <v>151.5483133464804</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>145.3837450136372</v>
+        <v>145.3718940089588</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>198.1660939580221</v>
+        <v>198.1493432941917</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>189.8411948762938</v>
+        <v>189.8252346045886</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>181.9080764318168</v>
+        <v>181.8928652496284</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>174.3463149381619</v>
+        <v>174.3318138909352</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>167.1366451237712</v>
+        <v>167.1228174612192</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>160.2608893557666</v>
+        <v>160.2477003975076</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>153.7018914893994</v>
+        <v>153.6893084993509</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>209.0896711833006</v>
+        <v>209.0719327082108</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>200.2743711753577</v>
+        <v>200.2574717624379</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>191.8749607666388</v>
+        <v>191.8588565089868</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>183.8697290553597</v>
+        <v>183.8543785444207</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>176.2381976773725</v>
+        <v>176.2235618498537</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>168.9610454537113</v>
+        <v>168.9470874485348</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>162.0200379651617</v>
+        <v>162.0067229897431</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>293.0799865722656</v>
+        <v>294.0199890136719</v>
       </c>
     </row>
     <row r="14">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.1010499911386181</v>
+        <v>0.1010598126993417</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>1.022105452369684</v>
+        <v>1.022107522678842</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>293.0799865722656</v>
+        <v>294.0199890136719</v>
       </c>
     </row>
     <row r="49">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>155.2994867037661</v>
+        <v>155.2866845839643</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>216.5622996397496</v>
+        <v>216.544347283912</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>108.748354243858</v>
+        <v>108.7394255960068</v>
       </c>
     </row>
     <row r="59">
